--- a/ig/test-tabs-svs/ValueSet-jdv-j329-public-activite-smsse-regulee-niv1-finess.xlsx
+++ b/ig/test-tabs-svs/ValueSet-jdv-j329-public-activite-smsse-regulee-niv1-finess.xlsx
@@ -128,7 +128,7 @@
     <t>used-codesystem</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r403-public-activite-smsse-regulee|20260223120000</t>
+    <t>https://smt.esante.gouv.fr/fhir/CodeSystem/tre-r403-public-activite-smsse-regulee|20260629120000</t>
   </si>
   <si>
     <t>version</t>
